--- a/Project StudentsPerformance_V1.xlsx
+++ b/Project StudentsPerformance_V1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cd3aed9e3b414e5/Desktop/Portofolio-Data Analyst/student-performance-analysis-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{991E0B6A-0312-44E8-81A2-1A0C17D7A8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AFB70AA-1BA1-4BAA-9E31-4C99280A58DD}"/>
+  <xr:revisionPtr revIDLastSave="414" documentId="13_ncr:1_{991E0B6A-0312-44E8-81A2-1A0C17D7A8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC991234-63A4-4A87-83A3-61FC1E52511E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{29823EF1-DD71-4387-9FAD-5D59B23BBA8C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{29823EF1-DD71-4387-9FAD-5D59B23BBA8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Project StudentsPerformance" sheetId="1" r:id="rId1"/>
@@ -14632,8 +14632,8 @@
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>77755</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -14648,8 +14648,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6812280" y="11116587"/>
-          <a:ext cx="12740640" cy="2843253"/>
+          <a:off x="6793619" y="10503566"/>
+          <a:ext cx="12705183" cy="2979169"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14725,6 +14725,64 @@
             <a:rPr lang="en-ID" sz="2000" b="1" i="1" baseline="0"/>
             <a:t>- Student with highest parental of education backgrounds tend to have slightly better academic performance</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-ID" sz="2000" b="1" i="1" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-ID" sz="2000" b="1" i="1" baseline="0"/>
+            <a:t>- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-ID" sz="2000" b="1" i="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Lunch type shows a noticeable relationship with academic performance</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-ID" sz="2000" b="1" i="1" baseline="0"/>
         </a:p>
         <a:p>
           <a:endParaRPr lang="en-ID" sz="2000" baseline="0"/>
